--- a/PasssengerData.xlsx
+++ b/PasssengerData.xlsx
@@ -2,42 +2,38 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uwacloud-my.sharepoint.com/personal/upundeer_univ-wea_com/Documents/Desktop/last_mile/backend/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uwacloud-my.sharepoint.com/personal/upundeer_univ-wea_com/Documents/Desktop/backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{AFBE08E5-F5CD-4ECF-B028-77ADB318EB3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0FD88E9-8EAF-4B33-9A87-5BA55CC0A718}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_7359173E4E2E0D2F38609C4D087596515122E011" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F6CD6FA-9CC7-43EB-AA16-2FC486093825}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{4ACD6E61-C622-46CA-BFC9-A8725EDF7E88}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
+  <si>
+    <t>_Pid</t>
+  </si>
+  <si>
+    <t>Airline_Name</t>
+  </si>
+  <si>
+    <t>Passenger_Name</t>
+  </si>
+  <si>
+    <t>Passenger_Contact</t>
+  </si>
   <si>
     <t>Departure</t>
   </si>
@@ -45,102 +41,79 @@
     <t>Arrival</t>
   </si>
   <si>
-    <t>_Pid</t>
+    <t>Call_Attempt_Success</t>
   </si>
   <si>
     <t>Boeing 737</t>
   </si>
   <si>
+    <t>Vaibhav Raj</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
     <t>Boeing 747</t>
   </si>
   <si>
+    <t>Utkarsh Pundeer</t>
+  </si>
+  <si>
     <t>Lockheed Martin F-35 Lightning II</t>
   </si>
   <si>
+    <t>Vivek Sharma</t>
+  </si>
+  <si>
     <t>McDonnell Douglas F/A-18 Hornet</t>
   </si>
   <si>
+    <t>Justin</t>
+  </si>
+  <si>
     <t>Lockheed Martin F-22 Raptor</t>
   </si>
   <si>
+    <t>Tim David</t>
+  </si>
+  <si>
     <t>Concorde</t>
   </si>
   <si>
+    <t>Donald Trump</t>
+  </si>
+  <si>
     <t>Hughes H-4 Hercules</t>
   </si>
   <si>
+    <t>Obama</t>
+  </si>
+  <si>
     <t>Boeing B-17 Flying Fortress</t>
   </si>
   <si>
+    <t>Jaskaran</t>
+  </si>
+  <si>
     <t>Supermarine Spitfire</t>
   </si>
   <si>
+    <t>Hanuma Vihari</t>
+  </si>
+  <si>
     <t>ATR 72</t>
   </si>
   <si>
-    <t>Vaibhav Raj</t>
-  </si>
-  <si>
-    <t>Utkarsh Pundeer</t>
-  </si>
-  <si>
-    <t>Vivek Sharma</t>
-  </si>
-  <si>
-    <t>Justin</t>
-  </si>
-  <si>
-    <t>Tim David</t>
-  </si>
-  <si>
-    <t>Donald Trump</t>
-  </si>
-  <si>
-    <t>Obama</t>
-  </si>
-  <si>
-    <t>Jaskaran</t>
-  </si>
-  <si>
-    <t>Hanuma Vihari</t>
-  </si>
-  <si>
     <t>Rahul</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Airline_Name</t>
-  </si>
-  <si>
-    <t>Passenger_Name</t>
-  </si>
-  <si>
-    <t>Passenger_Contact</t>
-  </si>
-  <si>
-    <t>Cab_Opted</t>
-  </si>
-  <si>
-    <t>Details_Sent_Status</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -167,23 +140,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -193,10 +157,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -515,311 +475,288 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F2666D8-DA3B-4386-9D2D-C639439F6DF5}">
-  <dimension ref="A1:H11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="31.33203125" customWidth="1"/>
-    <col min="3" max="3" width="17.77734375" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" customWidth="1"/>
-    <col min="7" max="7" width="12.5546875" customWidth="1"/>
-    <col min="8" max="8" width="18.77734375" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="19.5" customWidth="1"/>
+    <col min="4" max="4" width="19.296875" customWidth="1"/>
+    <col min="5" max="5" width="13.796875" customWidth="1"/>
+    <col min="6" max="6" width="16.796875" customWidth="1"/>
+    <col min="7" max="7" width="24.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="2">
-        <v>919058725624</v>
-      </c>
-      <c r="E2" s="3">
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2">
+        <v>919058725624</v>
+      </c>
+      <c r="E2">
         <v>0.64583333333333337</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2">
         <v>0.875</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="2">
-        <v>919058725624</v>
-      </c>
-      <c r="E3" s="3">
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3">
+        <v>919058725624</v>
+      </c>
+      <c r="E3">
         <v>0.6875</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3">
         <v>0.91666666666666696</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="2"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H4" s="2"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H6" s="2"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H7" s="2"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H8" s="2"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H9" s="2"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H11" s="2"/>
+      <c r="G3" t="s">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:H11" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2410102A-5D97-4AA5-96E5-64505B574367}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="2">
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1">
         <v>3</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1">
+        <v>919058725624</v>
+      </c>
+      <c r="E1">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="F1">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="G1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2">
+        <v>919058725624</v>
+      </c>
+      <c r="E2">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>5</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="2">
-        <v>919058725624</v>
-      </c>
-      <c r="E1" s="3">
-        <v>0.72916666666666696</v>
-      </c>
-      <c r="F1" s="3">
-        <v>0.95833333333333304</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3">
+        <v>919058725624</v>
+      </c>
+      <c r="E3">
+        <v>0.8125</v>
+      </c>
+      <c r="F3">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="G3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4">
+        <v>919058725624</v>
+      </c>
+      <c r="E4">
+        <v>0.85416666666666696</v>
+      </c>
+      <c r="F4">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5">
+        <v>919058725624</v>
+      </c>
+      <c r="E5">
+        <v>0.89583333333333304</v>
+      </c>
+      <c r="F5">
+        <v>1.125</v>
+      </c>
+      <c r="G5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>4</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="2">
-        <v>919058725624</v>
-      </c>
-      <c r="E2" s="3">
-        <v>0.77083333333333304</v>
-      </c>
-      <c r="F2" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="2">
-        <v>919058725624</v>
-      </c>
-      <c r="E3" s="3">
-        <v>0.8125</v>
-      </c>
-      <c r="F3" s="3">
-        <v>1.0416666666666701</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="2">
-        <v>919058725624</v>
-      </c>
-      <c r="E4" s="3">
-        <v>0.85416666666666696</v>
-      </c>
-      <c r="F4" s="3">
-        <v>1.0833333333333299</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>7</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="2">
-        <v>919058725624</v>
-      </c>
-      <c r="E5" s="3">
-        <v>0.89583333333333304</v>
-      </c>
-      <c r="F5" s="3">
-        <v>1.125</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>8</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="D6">
+        <v>919058725624</v>
+      </c>
+      <c r="E6">
+        <v>0.9375</v>
+      </c>
+      <c r="F6">
+        <v>1.1666666666666701</v>
+      </c>
+      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>919058725624</v>
+      </c>
+      <c r="E7">
+        <v>0.97916666666666696</v>
+      </c>
+      <c r="F7">
+        <v>1.2083333333333299</v>
+      </c>
+      <c r="G7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>10</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="2">
-        <v>919058725624</v>
-      </c>
-      <c r="E6" s="3">
-        <v>0.9375</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1.1666666666666701</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>9</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="2">
-        <v>919058725624</v>
-      </c>
-      <c r="E7" s="3">
-        <v>0.97916666666666696</v>
-      </c>
-      <c r="F7" s="3">
-        <v>1.2083333333333299</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>10</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="2">
-        <v>919058725624</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8">
+        <v>919058725624</v>
+      </c>
+      <c r="E8">
         <v>1.0208333333333299</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8">
         <v>1.25</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>23</v>
+      <c r="G8" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:G8" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>